--- a/samples/clover/design-data/xlsx/Progression.xlsx
+++ b/samples/clover/design-data/xlsx/Progression.xlsx
@@ -14,14 +14,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Ante!$B$2:$E$13]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Blind!$B$2:$F$7]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[BossBlind!$B$2:$G$32]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[BossBlind!$B$2:$H$32]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[BossEffect!$B$2:$BL$30]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="239">
   <si>
     <t xml:space="preserve">:table Ante(key=ante)</t>
   </si>
@@ -1283,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.328125" customWidth="1"/>
@@ -1292,6 +1292,7 @@
     <col min="5" max="5" width="18.75" customWidth="1"/>
     <col min="6" max="6" width="15.234375" customWidth="1"/>
     <col min="7" max="7" width="24.609375" customWidth="1"/>
+    <col min="8" max="8" width="15.234375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1306,6 +1307,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -1329,6 +1331,9 @@
       <c r="G2" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -1352,6 +1357,9 @@
       <c r="G3" s="4" t="s">
         <v>48</v>
       </c>
+      <c r="H3" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -1375,6 +1383,9 @@
       <c r="G4" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
@@ -1395,6 +1406,9 @@
       <c r="G5" s="5">
         <v>1</v>
       </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
@@ -1415,6 +1429,9 @@
       <c r="G6" s="6">
         <v>2</v>
       </c>
+      <c r="H6" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
@@ -1435,6 +1452,9 @@
       <c r="G7" s="5">
         <v>3</v>
       </c>
+      <c r="H7" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
@@ -1455,6 +1475,9 @@
       <c r="G8" s="6">
         <v>4</v>
       </c>
+      <c r="H8" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
@@ -1475,6 +1498,9 @@
       <c r="G9" s="5">
         <v>5</v>
       </c>
+      <c r="H9" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
@@ -1495,6 +1521,9 @@
       <c r="G10" s="6">
         <v>6</v>
       </c>
+      <c r="H10" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
@@ -1515,6 +1544,9 @@
       <c r="G11" s="5">
         <v>7</v>
       </c>
+      <c r="H11" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
@@ -1535,6 +1567,9 @@
       <c r="G12" s="6">
         <v>8</v>
       </c>
+      <c r="H12" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
@@ -1555,6 +1590,9 @@
       <c r="G13" s="5">
         <v>9</v>
       </c>
+      <c r="H13" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
@@ -1575,6 +1613,9 @@
       <c r="G14" s="6">
         <v>10</v>
       </c>
+      <c r="H14" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
@@ -1595,6 +1636,9 @@
       <c r="G15" s="5">
         <v>11</v>
       </c>
+      <c r="H15" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
@@ -1615,6 +1659,9 @@
       <c r="G16" s="6">
         <v>12</v>
       </c>
+      <c r="H16" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
@@ -1635,6 +1682,9 @@
       <c r="G17" s="5">
         <v>13</v>
       </c>
+      <c r="H17" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
@@ -1655,6 +1705,9 @@
       <c r="G18" s="6">
         <v>14</v>
       </c>
+      <c r="H18" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
@@ -1675,6 +1728,9 @@
       <c r="G19" s="5">
         <v>15</v>
       </c>
+      <c r="H19" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
@@ -1695,6 +1751,9 @@
       <c r="G20" s="6">
         <v>16</v>
       </c>
+      <c r="H20" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
@@ -1715,6 +1774,9 @@
       <c r="G21" s="5">
         <v>17</v>
       </c>
+      <c r="H21" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
@@ -1735,6 +1797,9 @@
       <c r="G22" s="6">
         <v>18</v>
       </c>
+      <c r="H22" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
@@ -1755,6 +1820,9 @@
       <c r="G23" s="5">
         <v>19</v>
       </c>
+      <c r="H23" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
@@ -1775,6 +1843,9 @@
       <c r="G24" s="6">
         <v>20</v>
       </c>
+      <c r="H24" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
@@ -1795,6 +1866,9 @@
       <c r="G25" s="5">
         <v>21</v>
       </c>
+      <c r="H25" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
@@ -1815,6 +1889,9 @@
       <c r="G26" s="6">
         <v>22</v>
       </c>
+      <c r="H26" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
@@ -1835,6 +1912,9 @@
       <c r="G27" s="5">
         <v>23</v>
       </c>
+      <c r="H27" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
@@ -1855,6 +1935,9 @@
       <c r="G28" s="6">
         <v>24</v>
       </c>
+      <c r="H28" s="6">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
@@ -1875,6 +1958,9 @@
       <c r="G29" s="5">
         <v>25</v>
       </c>
+      <c r="H29" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
@@ -1895,6 +1981,9 @@
       <c r="G30" s="6">
         <v>26</v>
       </c>
+      <c r="H30" s="6">
+        <v>8</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
@@ -1915,6 +2004,9 @@
       <c r="G31" s="5">
         <v>27</v>
       </c>
+      <c r="H31" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
@@ -1935,9 +2027,12 @@
       <c r="G32" s="6">
         <v>28</v>
       </c>
+      <c r="H32" s="6">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G32"/>
+  <autoFilter ref="B2:H32"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/samples/clover/design-data/xlsx/Progression.xlsx
+++ b/samples/clover/design-data/xlsx/Progression.xlsx
@@ -15,13 +15,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Ante!$B$2:$E$13]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Blind!$B$2:$F$7]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[BossBlind!$B$2:$H$32]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[BossEffect!$B$2:$BL$30]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[BossEffect!$B$2:$BM$30]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="240">
   <si>
     <t xml:space="preserve">:table Ante(key=ante)</t>
   </si>
@@ -543,6 +543,9 @@
   </si>
   <si>
     <t xml:space="preserve">operation.handler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operation.sticker</t>
   </si>
   <si>
     <t xml:space="preserve">foreign BossBlind</t>
@@ -2039,7 +2042,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL30"/>
+  <dimension ref="A1:BM30"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="44.53125" customWidth="1"/>
@@ -2089,7 +2092,7 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2161,6 +2164,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -2355,43 +2359,46 @@
       <c r="BL2" s="4" t="s">
         <v>173</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -2408,7 +2415,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -2447,43 +2454,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -2500,7 +2508,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -2539,6 +2547,7 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
@@ -2548,34 +2557,34 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AU5" s="5">
         <v>2</v>
@@ -2589,40 +2598,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BA6" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BD6" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
@@ -2633,40 +2642,40 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH7" s="5">
         <v>1</v>
       </c>
       <c r="BF7" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -2677,40 +2686,40 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BA8" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BD8" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -2721,40 +2730,40 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BA9" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BD9" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -2765,40 +2774,40 @@
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH10" s="6">
         <v>-1</v>
       </c>
       <c r="BF10" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2809,37 +2818,37 @@
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BD11" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -2850,40 +2859,40 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BA12" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="BD12" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -2894,34 +2903,34 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14">
@@ -2932,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E14" s="6">
         <v>1</v>
@@ -2941,25 +2950,25 @@
         <v>7</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15">
@@ -2970,37 +2979,37 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AR15" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AS15" s="5">
         <v>-1</v>
@@ -3014,34 +3023,34 @@
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
@@ -3052,43 +3061,43 @@
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH17" s="5">
         <v>1</v>
       </c>
       <c r="BF17" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="BH17" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18">
@@ -3099,40 +3108,40 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH18" s="6">
         <v>1</v>
       </c>
       <c r="BF18" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19">
@@ -3143,40 +3152,40 @@
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
       </c>
       <c r="BF19" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="BG19" s="5" t="s">
         <v>33</v>
@@ -3190,40 +3199,40 @@
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
       </c>
       <c r="BF20" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21">
@@ -3234,37 +3243,37 @@
         <v>0</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AV21" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22">
@@ -3275,40 +3284,40 @@
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH22" s="6">
         <v>1</v>
       </c>
       <c r="BF22" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23">
@@ -3319,40 +3328,40 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG23" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AH23" s="5">
         <v>-1</v>
@@ -3366,37 +3375,37 @@
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BD24" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
@@ -3407,40 +3416,40 @@
         <v>0</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH25" s="5">
         <v>1</v>
       </c>
       <c r="BF25" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
@@ -3451,34 +3460,34 @@
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AD26" s="6">
         <v>0</v>
@@ -3492,34 +3501,34 @@
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28">
@@ -3530,40 +3539,40 @@
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH28" s="6">
         <v>1</v>
       </c>
       <c r="BF28" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29">
@@ -3574,34 +3583,34 @@
         <v>0</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA29" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30">
@@ -3612,44 +3621,44 @@
         <v>0</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA30" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH30" s="6">
         <v>1</v>
       </c>
       <c r="BF30" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL30"/>
+  <autoFilter ref="B2:BM30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>